--- a/docs/design/IISM-UI-Review.xlsx
+++ b/docs/design/IISM-UI-Review.xlsx
@@ -175,7 +175,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sprint 69, 'scannable jobs': UI-04, 05, 06, 07, 08, 09, 10, 11, 17. Then Sprint 70, 'a candidate's first minute': UI-01, 02, 12, 13, 19. Brand-dependent: UI-03, 18, 20, 23, 24, 27.</t>
+          <t xml:space="preserve">Sprint 69, 'scannable jobs', is done (9 findings; see the Status column). Next, Sprint 70, 'a candidate's first minute': UI-01, 02, 12, 13, 19. Brand-dependent: UI-03, 18, 20, 23, 24, 27.</t>
         </is>
       </c>
     </row>
@@ -224,6 +224,7 @@
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="60" customWidth="1"/>
     <col min="11" max="11" width="50" customWidth="1"/>
+    <col min="12" max="12" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -282,6 +283,11 @@
           <t xml:space="preserve">Files</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
@@ -339,6 +345,11 @@
           <t xml:space="preserve">web/src/components/Hero.tsx, RoleChooser.tsx, StatsBand.tsx, HowItWorks.tsx, web/src/app/[locale]/page.tsx</t>
         </is>
       </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
@@ -396,6 +407,11 @@
           <t xml:space="preserve">web/src/messages/en.json and hi.json (hero, framework, howItWorks namespaces)</t>
         </is>
       </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -453,6 +469,11 @@
           <t xml:space="preserve">web/src/app/globals.css (tokens), web/public/, mobile/assets/</t>
         </is>
       </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -510,6 +531,11 @@
           <t xml:space="preserve">web/src/components/JobBrowser.tsx, web/src/components/ui/badge.tsx, mobile/app/(tabs)/jobs.tsx</t>
         </is>
       </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in Sprint 69 (web and phone): title, employer with a verified mark, place, pay, how soon it closes; the NSQF badge and the generated sentence are gone from the card. Still open: the match score on a signed-in card.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -567,6 +593,11 @@
           <t xml:space="preserve">web/src/lib/format.ts, mobile/src/core/format.ts (formatInr), job card and detail components</t>
         </is>
       </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in Sprint 69 (web and phone): 'about Rs 18,300-25,000 a month' on cards and on the vacancy, the yearly figure beneath it on the vacancy. A gig keeps its posted figure. Rule shared by one fixture (tests/fixtures/pay_cases.json).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -624,6 +655,11 @@
           <t xml:space="preserve">web/src/components/JobBrowser.tsx, CourseBrowser.tsx, api/modules/marketplace/routes.py (offset and total already exist)</t>
         </is>
       </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in Sprint 69 (web): 24 at a time, the server's total, 'Show more (n left)', a state filter that is the catalogue's own (GET /jobs/states). The phone already paged.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -681,6 +717,11 @@
           <t xml:space="preserve">web/src/components/ui/badge.tsx and the text-[11px] classes</t>
         </is>
       </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in Sprint 69 (web): nothing under 12 px (35 literal sizes and the 2xs step), held by src/lib/type-floor.test.ts.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -738,6 +779,11 @@
           <t xml:space="preserve">web/src/components/ApplyPanel.tsx and the job page; mobile/src/ui/ApplyPanel.tsx</t>
         </is>
       </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in Sprint 69 (web and phone): a bar under the content that follows the person, Apply and Save side by side; none for an account that cannot apply. The match screen keeps its place on purpose.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -795,6 +841,11 @@
           <t xml:space="preserve">web/src/components/SkillRequirements.tsx, mobile job detail, api listing serialiser (de-duplicate at display)</t>
         </is>
       </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in Sprint 69 (web and phone, vacancy only): each standard once, sentence case, the generic ones under 'Also covered', a 'Must have' chip instead of a score. The standard's own page is unchanged.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -852,6 +903,11 @@
           <t xml:space="preserve">web/src/components/ReportListing.tsx and the job and course pages</t>
         </is>
       </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in Sprint 69 for vacancies: 'Verified employer' or 'Not yet verified' and 'Never pay to apply' with a way to report; the slug line is gone (also from the course page). A course page has no strip yet.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -909,6 +965,11 @@
           <t xml:space="preserve">web/src/components/Header.tsx, Footer.tsx, web/src/components/ui/button-variants.ts, web/e2e/support/test.ts (add a target-size check)</t>
         </is>
       </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in Sprint 69 (web): a 44 px floor on buttons, the header and the footer, checked on every page of the browser sweep (header and footer only; the rest of a page is still a count).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -966,6 +1027,11 @@
           <t xml:space="preserve">web/src/components/MatchBrowser.tsx, CandidateDashboard.tsx</t>
         </is>
       </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -1023,6 +1089,11 @@
           <t xml:space="preserve">web/src/components/MatchBrowser.tsx, GapPanel.tsx, charts/; mobile/src/ui/match.tsx</t>
         </is>
       </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -1080,6 +1151,11 @@
           <t xml:space="preserve">web/src/components/charts/status-funnel.tsx, ranked-bar-list.tsx</t>
         </is>
       </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -1137,6 +1213,11 @@
           <t xml:space="preserve">web/src/components/employer/ (vacancy list)</t>
         </is>
       </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -1194,6 +1275,11 @@
           <t xml:space="preserve">web/src/app/[locale]/admin/page.tsx and web/src/components/ops/</t>
         </is>
       </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -1251,6 +1337,11 @@
           <t xml:space="preserve">web/src/components/ops/ (queue), api/modules/operations/routes.py and service.py (return a total)</t>
         </is>
       </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed in Sprint 69: both operator queues return their true size; the screen says 'Showing 100 of 162' and offers the rest.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -1308,6 +1399,11 @@
           <t xml:space="preserve">mobile/app/(tabs)/_layout.tsx, mobile/src/ui/, a shared icon sprite</t>
         </is>
       </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -1365,6 +1461,11 @@
           <t xml:space="preserve">mobile/app/(tabs)/index.tsx</t>
         </is>
       </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -1422,6 +1523,11 @@
           <t xml:space="preserve">mobile/app/(tabs)/me.tsx</t>
         </is>
       </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -1479,6 +1585,11 @@
           <t xml:space="preserve">mobile/app/(tabs)/me.tsx, mobile/src/ui/list.tsx</t>
         </is>
       </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -1536,6 +1647,11 @@
           <t xml:space="preserve">mobile/app/profile.tsx</t>
         </is>
       </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -1593,6 +1709,11 @@
           <t xml:space="preserve">mobile/assets/*, mobile/app.json</t>
         </is>
       </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -1650,6 +1771,11 @@
           <t xml:space="preserve">web/src/components/ui/card.tsx, globals.css tokens; mobile/src/ui/list.tsx (Card)</t>
         </is>
       </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -1707,6 +1833,11 @@
           <t xml:space="preserve">web/src/app/globals.css, mobile/src/theme/index.tsx, scripts/sync_mobile_tokens.py</t>
         </is>
       </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -1764,6 +1895,11 @@
           <t xml:space="preserve">api/modules/marketplace (bulk and publishing defaults), job and course cards</t>
         </is>
       </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -1821,6 +1957,11 @@
           <t xml:space="preserve">web/src/components/ui/skeleton.tsx, mobile/src/ui/list.tsx</t>
         </is>
       </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -1878,6 +2019,11 @@
           <t xml:space="preserve">web/src/components/SignInForm.tsx, SignUpForm.tsx, Header.tsx</t>
         </is>
       </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -1935,9 +2081,14 @@
           <t xml:space="preserve">mobile/app/match/[slug].tsx, mobile/src/test/matches.test.tsx</t>
         </is>
       </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K30"/>
+  <autoFilter ref="A1:L30"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/design/IISM-UI-Review.xlsx
+++ b/docs/design/IISM-UI-Review.xlsx
@@ -175,7 +175,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sprint 69, 'scannable jobs', is done (9 findings; see the Status column). Next, Sprint 70, 'a candidate's first minute': UI-01, 02, 12, 13, 19. Brand-dependent: UI-03, 18, 20, 23, 24, 27.</t>
+          <t xml:space="preserve">Sprints 69 ('scannable jobs') and 70 ('a candidate's first minute') are done (14 findings; see the Status column). Brand-dependent and open: UI-03, 18, 20, 23, 24, 27.</t>
         </is>
       </c>
     </row>
@@ -347,7 +347,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in Sprint 70 (web): the search first with five one-tap example jobs, the chooser under it, two small links for employers and providers. The 'three sides' cards and the framework band are off the homepage (the framework band is on About). The live people figures and the browse counts stay, by the owner's choice.</t>
         </is>
       </c>
     </row>
@@ -409,7 +409,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in Sprint 70 (web, and the phone home's words): the hero, how it works and the browse panels no longer say NSQF, framework or taxonomy, held by a test in English, Hindi and Malay. The Hindi was written by the engineer and needs a native reader.</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in Sprint 70 (web): a one-line strip ('14 matches, best 87, profile 100% complete'), the charts one tap behind 'Your numbers', five cards then 'Show more'. Also fixed on the way: /me/matches answered total as the length of the page.</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in Sprint 70 (web and phone): each match says in a sentence what the person has and lacks, with one main action; the lists, codes and level scale are behind Details. The sentence leaves out the generic standards the score still counts, and says so.</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in Sprint 70 (phone): a signed-in seeker's home shows the best match with its sentence, profile completeness and the next step, new updates, and the applications an employer acted on in the last 14 days. Applying is not offered there: the match summary has no employer name for the consent step to name.</t>
         </is>
       </c>
     </row>

--- a/docs/design/IISM-UI-Review.xlsx
+++ b/docs/design/IISM-UI-Review.xlsx
@@ -175,7 +175,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sprints 69 ('scannable jobs') and 70 ('a candidate's first minute') are done (14 findings; see the Status column). Brand-dependent and open: UI-03, 18, 20, 23, 24, 27.</t>
+          <t xml:space="preserve">Sprints 69 ('scannable jobs') and 70 ('a candidate's first minute') are done (18 findings; see the Status column). Brand-dependent and open: UI-03, 18, 20, 23, 24, 27.</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in Sprint 73 (web): the funnel's count leads and its bar supports it, and a line above the by-vacancy list says amber is 'new applications waiting' and blue 'none waiting'. The funnel already scaled to its first step (the finding saw genuinely equal counts), so its widths are unchanged.</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in Sprint 73 (web): one primary action per row (See candidates for a live vacancy, Publish for a draft; the interested learners for a live course), Edit beside it, the rest behind 'More' (a native details, RowActions). Targets under 44 px on a phone: employer-home 52 to 0, provider-home 69 to 0.</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in Sprint 73 (web): a section nav (eight anchors, tier-aware, 44 px), the three daily queues open first, and four reference panels (programmes, skill gap, aliases, enrolment) folded and loaded only when opened. /admin 40.2 to 27.9 screens on a phone (31.2 to 24.8 on desktop), targets under 44 px 181 to 0, first-load JS 698,039 to 686,248 bytes (headroom 1,961 to 13,752). The two long queues are still long.</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in Sprint 73 (the finding was mis-stated): bulk upload never inherited a generated description (a blank cell stores none). The boilerplate was 129 job and 129 course descriptions in the demonstration seed, which now writes none for them; the bulk check says once, for the file, how many rows have no description or a very short one; the editors say what to write. Not built: refusing to publish with none (a new 422 on a released operation).</t>
         </is>
       </c>
     </row>

--- a/docs/design/IISM-UI-Review.xlsx
+++ b/docs/design/IISM-UI-Review.xlsx
@@ -175,7 +175,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sprints 69 ('scannable jobs') and 70 ('a candidate's first minute') are done (18 findings; see the Status column). Brand-dependent and open: UI-03, 18, 20, 23, 24, 27.</t>
+          <t xml:space="preserve">Sprints 69 to 73 and Epic B19 (Sprints 76 to 90) are done (27 of 29 findings; see the Status column). Open, and the owner's: UI-03 (imagery and brand art) and UI-23 (launcher art).</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in Sprint 82 (phone): five icons beside the words (Home, Briefcase, BookOpen, Target, User), the unread count a badge on the Me icon, and the spoken name still carries the exact number. The bar is 64 dp plus the inset because the navigator's default cut the labels off.</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in Sprint 82 (phone): Me is two groups of rows with an icon, a chevron and at least 56 dp each, named by the title; Sign out is not the same weight as My applications.</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in Sprints 78 and 83 (phone): the browser run scores layout shift (capture-app.mjs, CHECK=1), the signed-in home waits for its four queries and is held at a measured height, and the shift went from 0.169 to 0.002 with every screen held to 0.1. Measured in a browser build, not on a device.</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in Sprint 83 (phone): a progress header (a progressbar with its value) and four sections, each form section with its own Save named for the section ('Save: About you') and its own saved notice. Not built: a single 'Next' action; the history sections are rows that open the editor.</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in Sprint 80 and used in Sprints 84 to 89 (web): Card levels (default, raised, inset, interactive), a tinted page with white cards, a primary and a soft button, and every card family on one shape (job, course, standard, application, interest, saved job). The rule 'an inset is a box inside a card, never a Card in a Card' is held by the gallery and the reviews of each family; nothing mechanical forbids a nested Card.</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in Sprint 77 (web and phone): a six-step named type scale (caption 13, small 15, body 16, lead 18, title 24, display 30) in globals.css, mapped onto Tailwind's own text-* names so no call site changed, with taller Devanagari line heights, shared with the phone through the token sync. Secondary text is 15 px and the floor stays 12 px.</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in Sprint 80, in part (web): EmptyState (an icon in a tinted disc, a sentence, a reason and the next step) on the ten page-level empty lists, a Spinner, and no toast. Not done: an illustration (the slot exists; the art is the owner's) and the small inline empties, which are still one sentence.</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in Sprints 79, 81 and 86 (web): a reduced header on sign-in and sign-up (logo and language), 44 px controls ('Skip for now', the back links, the consent row), and the page you are on marked in the navigation. The language select is 44 px.</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in Sprint 68 (phone), the one product change the review made: the courses section and the budget field show only when something is missing, with a test that fails without it.</t>
         </is>
       </c>
     </row>
